--- a/.github/skills/excel-quote-writer/assets/summary-layout-template.xlsx
+++ b/.github/skills/excel-quote-writer/assets/summary-layout-template.xlsx
@@ -1,37 +1,357 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workshop\Azure Quote Agent\.github\skills\excel-quote-writer\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172E58EE-0BE6-42DB-AF1C-6EB6923EFB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LineItems" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Evidence" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="LineItems" sheetId="2" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
+    <sheet name="Evidence" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
+  <si>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>Quote Summary</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Customer / Project</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Competitor Cloud</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>Pricing Source Date</t>
+  </si>
+  <si>
+    <t>Monthly Cost Comparison (USD)</t>
+  </si>
+  <si>
+    <t>PayGo</t>
+  </si>
+  <si>
+    <t>1Y RI</t>
+  </si>
+  <si>
+    <t>3Y RI</t>
+  </si>
+  <si>
+    <t>Competitor (Original)</t>
+  </si>
+  <si>
+    <t>Azure (Mapped)</t>
+  </si>
+  <si>
+    <t>Delta (Azure - Comp.)</t>
+  </si>
+  <si>
+    <t>Delta %</t>
+  </si>
+  <si>
+    <t>resource_type</t>
+  </si>
+  <si>
+    <t>region_azure</t>
+  </si>
+  <si>
+    <t>primary_sku</t>
+  </si>
+  <si>
+    <t>fallback_skus</t>
+  </si>
+  <si>
+    <t>sap_sku</t>
+  </si>
+  <si>
+    <t>billing_unit</t>
+  </si>
+  <si>
+    <t>unit_price_AWS_paygo</t>
+  </si>
+  <si>
+    <t>unit_price_Azure_paygo</t>
+  </si>
+  <si>
+    <t>review_flag</t>
+  </si>
+  <si>
+    <t>review_reason</t>
+  </si>
+  <si>
+    <t>evidence_id</t>
+  </si>
+  <si>
+    <t>linux</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>southeastasia</t>
+  </si>
+  <si>
+    <t>Standard_E4as_v5</t>
+  </si>
+  <si>
+    <t>Standard_E4s_v5,Standard_E4ds_v5</t>
+  </si>
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>ev-1</t>
+  </si>
+  <si>
+    <t>sku/os</t>
+  </si>
+  <si>
+    <t>item_1</t>
+  </si>
+  <si>
+    <t>EC2</t>
+  </si>
+  <si>
+    <t>item_2</t>
+  </si>
+  <si>
+    <t>General Purpose (gp3) provisioned storage</t>
+  </si>
+  <si>
+    <t>Asia Pacific (Tokyo)</t>
+  </si>
+  <si>
+    <t>japaneast</t>
+  </si>
+  <si>
+    <t>GB/month</t>
+  </si>
+  <si>
+    <t>monthly_cost_AWS_paygo</t>
+  </si>
+  <si>
+    <t>monthly_cost_Azure_paygo</t>
+  </si>
+  <si>
+    <t>monthly_cost_AWS_1YRI</t>
+  </si>
+  <si>
+    <t>monthly_cost_AWS_3YRI</t>
+  </si>
+  <si>
+    <t>monthly_cost_Azure_1YRI</t>
+  </si>
+  <si>
+    <t>monthly_cost_Azure_3YRI</t>
+  </si>
+  <si>
+    <t>assumption_id</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>statement</t>
+  </si>
+  <si>
+    <t>impact_scope</t>
+  </si>
+  <si>
+    <t>requires_confirmation</t>
+  </si>
+  <si>
+    <t>A-1</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>all rows with empty os</t>
+  </si>
+  <si>
+    <t>A-2</t>
+  </si>
+  <si>
+    <t>all rows with empty region</t>
+  </si>
+  <si>
+    <t>A-3</t>
+  </si>
+  <si>
+    <t>pricing</t>
+  </si>
+  <si>
+    <t>all priced rows</t>
+  </si>
+  <si>
+    <t>A-4</t>
+  </si>
+  <si>
+    <t>mapping</t>
+  </si>
+  <si>
+    <t>disk_redundancy_default=LRS</t>
+  </si>
+  <si>
+    <t>subset rows</t>
+  </si>
+  <si>
+    <t>A-5</t>
+  </si>
+  <si>
+    <t>gp2_default_map=Premium SSD Managed Disks</t>
+  </si>
+  <si>
+    <t>A-6</t>
+  </si>
+  <si>
+    <t>gp3_default_iops=3000_applied</t>
+  </si>
+  <si>
+    <t>A-7</t>
+  </si>
+  <si>
+    <t>gp3_default_iops=3000_when_missing</t>
+  </si>
+  <si>
+    <t>A-8</t>
+  </si>
+  <si>
+    <t>gp3_default_throughput_mbps=125_applied</t>
+  </si>
+  <si>
+    <t>A-9</t>
+  </si>
+  <si>
+    <t>gp3_default_throughput_mbps=125_when_missing</t>
+  </si>
+  <si>
+    <t>A-10</t>
+  </si>
+  <si>
+    <t>hours_in_month_default=730</t>
+  </si>
+  <si>
+    <t>default VM OS: Linux</t>
+  </si>
+  <si>
+    <t>default region: eastus</t>
+  </si>
+  <si>
+    <t>default currency: USD</t>
+  </si>
+  <si>
+    <t>source_type</t>
+  </si>
+  <si>
+    <t>source_url</t>
+  </si>
+  <si>
+    <t>fetched_at</t>
+  </si>
+  <si>
+    <t>mapping_version</t>
+  </si>
+  <si>
+    <t>policy_version</t>
+  </si>
+  <si>
+    <t>kb_version</t>
+  </si>
+  <si>
+    <t>price_date</t>
+  </si>
+  <si>
+    <t>source_ref</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>retail_api</t>
+  </si>
+  <si>
+    <t>https://prices.azure.com/api/retail/prices?$filter=serviceName eq 'Virtual Machines' and armRegionName eq 'southeastasia' and armSkuName eq 'Standard_E4as_v5'</t>
+  </si>
+  <si>
+    <t>2026-02-28T10:23:55+00:00</t>
+  </si>
+  <si>
+    <t>v1</t>
+  </si>
+  <si>
+    <t>{'file_name': 'sample_input_3_vm_disk.xlsx', 'sheet': 'Sheet1', 'row': 2, 'columns': ['A', 'B', 'C', 'D', 'E', 'F', 'G']}</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>item-1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,81 +369,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -411,115 +690,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="26.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="2"/>
+      <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:D9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:V3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>provider</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>unit_price_hourly</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>monthly_hours</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>monthly_cost</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="N2">
+        <v>221.92</v>
+      </c>
+      <c r="O2">
+        <v>198.56</v>
+      </c>
+      <c r="P2">
+        <v>140.16</v>
+      </c>
+      <c r="Q2">
+        <v>95.63000000000001</v>
+      </c>
+      <c r="R2">
+        <v>117.1666666666667</v>
+      </c>
+      <c r="S2">
+        <v>75.444444444444443</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3">
+        <v>500</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -528,34 +992,202 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -564,32 +1196,100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="132.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="86" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.46484375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ref</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>